--- a/omip_futuros_20260824.xlsx
+++ b/omip_futuros_20260824.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,79 +429,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Contract name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Best bid (€/MWh)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Best Ask (€/MWh)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Volume (MWh)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Price (€/MWh)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Volume (MWh)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr"/>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Open Interest</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nr of Contracts</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>OTC volume (MWh)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr"/>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>D (€/MWh)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>D-1 (€/MWh)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr"/>
+      <c r="R1" s="1" t="inlineStr"/>
+      <c r="S1" s="1" t="inlineStr"/>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Transparency info</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Fecha_Extraccion</t>
         </is>

--- a/omip_futuros_20260824.xlsx
+++ b/omip_futuros_20260824.xlsx
@@ -546,7 +546,11 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>0</t>
@@ -560,7 +564,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>120.35</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -617,7 +621,11 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>0</t>
@@ -631,7 +639,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>114.00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -688,7 +696,11 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>0</t>
@@ -702,7 +714,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>110.14</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -759,7 +771,11 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>0</t>
@@ -773,7 +789,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>107.52</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -830,7 +846,11 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>0</t>
@@ -844,7 +864,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>94.53</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -901,7 +921,11 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>0</t>
@@ -915,7 +939,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">

--- a/omip_futuros_20260824.xlsx
+++ b/omip_futuros_20260824.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,80 +425,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contract name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr"/>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Best bid (€/MWh)</t>
+          <t>Session Info</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Best Ask (€/MWh)</t>
+          <t>Session Info.1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Volume (MWh)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr"/>
+          <t>Session Info.2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Price (€/MWh)</t>
+          <t>Last Deal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Last Deal.1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Volume (MWh)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr"/>
+          <t>Last Deal.2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 9</t>
+        </is>
+      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Open Interest</t>
+          <t>End of day info</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Nr of Contracts</t>
+          <t>End of day info.1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>OTC volume (MWh)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr"/>
+          <t>End of day info.2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>D (€/MWh)</t>
+          <t>Reference prices</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>D-1 (€/MWh)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr"/>
-      <c r="R1" s="1" t="inlineStr"/>
-      <c r="S1" s="1" t="inlineStr"/>
+          <t>Reference prices.1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 17</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Transparency info</t>
+          <t>Unnamed: 19</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -510,72 +538,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ISIN Code: PTFTO0461841Nominal Fixo MWH: 24Trading last day: 2026-08-24Trading quotation: €/MWhFTB D Tu25Aug-26</t>
+          <t>Contract name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>Best bid (€/MWh)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>Best Ask (€/MWh)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Volume (MWh)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>Price (€/MWh)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>n.a.</t>
+          <t>Volume (MWh)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Open Interest</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Nr of Contracts</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OTC volume (MWh)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>120.35</t>
+          <t>D (€/MWh)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>106.65</t>
+          <t>D-1 (€/MWh)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Transparency info</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
@@ -583,70 +615,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ISIN Code: PTFTO0461858Nominal Fixo MWH: 24Trading last day: 2026-08-25Trading quotation: €/MWhFTB D We26Aug-26</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>105.39</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -660,7 +644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ISIN Code: PTFTO0461866Nominal Fixo MWH: 24Trading last day: 2026-08-26Trading quotation: €/MWhFTB D Th27Aug-26</t>
+          <t>ISIN Code: PTFTO0461841Nominal Fixo MWH: 24Trading last day: 2026-08-24Trading quotation: €/MWhFTB D Tu25Aug-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -714,12 +698,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>120.35</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>106.65</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -733,70 +717,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ISIN Code: PTFTO0461874Nominal Fixo MWH: 24Trading last day: 2026-08-27Trading quotation: €/MWhFTB D Fr28Aug-26</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>107.52</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>102.65</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -810,7 +746,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ISIN Code: PTFTO0461882Nominal Fixo MWH: 24Trading last day: 2026-08-28Trading quotation: €/MWhFTB D Sa29Aug-26</t>
+          <t>ISIN Code: PTFTO0461858Nominal Fixo MWH: 24Trading last day: 2026-08-25Trading quotation: €/MWhFTB D We26Aug-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -864,12 +800,12 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>94.53</t>
+          <t>114.00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -883,70 +819,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ISIN Code: PTFTO0461890Nominal Fixo MWH: 24Trading last day: 2026-08-28Trading quotation: €/MWhFTB D Su30Aug-26</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>85.53</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>80.66</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -957,6 +845,414 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ISIN Code: PTFTO0461866Nominal Fixo MWH: 24Trading last day: 2026-08-26Trading quotation: €/MWhFTB D Th27Aug-26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>110.14</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>105.27</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ISIN Code: PTFTO0461874Nominal Fixo MWH: 24Trading last day: 2026-08-27Trading quotation: €/MWhFTB D Fr28Aug-26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>107.52</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>102.65</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ISIN Code: PTFTO0461882Nominal Fixo MWH: 24Trading last day: 2026-08-28Trading quotation: €/MWhFTB D Sa29Aug-26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>94.53</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>89.66</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ISIN Code: PTFTO0461890Nominal Fixo MWH: 24Trading last day: 2026-08-28Trading quotation: €/MWhFTB D Su30Aug-26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>85.53</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>80.66</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
